--- a/data/trans_orig/IP1004-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1004-Edad-trans_orig.xlsx
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>248776</t>
+          <t>249082</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>502143</t>
+          <t>502438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123167</t>
+          <t>123900</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265030</t>
+          <t>265025</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>190195</t>
+          <t>190024</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200336</t>
+          <t>200622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>394207</t>
+          <t>393547</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>399476</t>
+          <t>399475</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>676678</t>
+          <t>676774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>715814</t>
+          <t>714969</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>721513</t>
+          <t>721434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1394747</t>
+          <t>1394933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401803</t>
+          <t>1401718</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>263376</t>
+          <t>263909</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>497280</t>
+          <t>497855</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150082</t>
+          <t>150110</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154207</t>
+          <t>153983</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>307903</t>
+          <t>308675</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172824</t>
+          <t>173672</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344971</t>
+          <t>345031</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>791</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>702969</t>
+          <t>701968</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>741068</t>
+          <t>741659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>747397</t>
+          <t>747393</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1447207</t>
+          <t>1447028</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1454215</t>
+          <t>1454279</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206013</t>
+          <t>205830</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>464431</t>
+          <t>463661</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>699095</t>
+          <t>699595</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1444861</t>
+          <t>1444503</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1004-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1004-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4140</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1322</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4674</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4075</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1322</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4523</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>252434</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>249616</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>252434</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>249082</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>502438</t>
+          <t>502886</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>732</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3648</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3656</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4252</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>732</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4038</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>126816</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>123900</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>123892</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,43%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,14%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,13%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>402</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265025</t>
+          <t>264811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1933</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5384</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>683</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4073</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3829</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>594</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5427</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>663</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>6435</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>204116</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>200665</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>205456</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>193414</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>190024</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>190268</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,65%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>204116</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>200622</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>205455</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,37%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>592</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>393547</t>
+          <t>393711</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>399475</t>
+          <t>399483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7372</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1415</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4247</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4515</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3255</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1266</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7731</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>719445</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>715328</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>721513</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,84%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679606</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>676774</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>676506</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,79%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>719445</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>714969</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>721434</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2097</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1394933</t>
+          <t>1394329</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401718</t>
+          <t>1401992</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,107 +3012,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4460</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>744</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3192</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4319</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3721</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>266357</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>262641</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>266357</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>263909</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>497855</t>
+          <t>497257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3360,102 +3360,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4227</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4724</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3961</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1568</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4588</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5454</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1568</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4730</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157794</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154344</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154044</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>150110</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>150873</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,49%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,95%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>157794</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>153983</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,11%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>446</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>308675</t>
+          <t>307951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,107 +3698,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4666</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>857</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4285</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4279</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4263</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>177100</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>173291</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>177100</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>173672</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>345031</t>
+          <t>345015</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6347</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4960</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4559</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>749</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6483</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>853</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>745763</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>741795</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>747397</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>706138</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>701968</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>702369</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,89%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>745763</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>741659</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>747393</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2080</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1447028</t>
+          <t>1446790</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1454279</t>
+          <t>1454217</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,94%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4729,47 +4729,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,92 +4959,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1360</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4687</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4369</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1360</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>209157</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>205830</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>206148</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,92%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>710</t>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>463661</t>
+          <t>463654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5415,47 +5415,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5758,47 +5758,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,92 +5988,92 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1360</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4776</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5576</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1360</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1059</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>703011</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>699595</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>698795</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2124</t>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1444503</t>
+          <t>1444390</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
